--- a/execution-substrates/csv/rulebook.xlsx
+++ b/execution-substrates/csv/rulebook.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:AP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -453,24 +453,40 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="29" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="23" customWidth="1" min="24" max="24"/>
-    <col width="26" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="29" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="21" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="21" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="29" customWidth="1" min="36" max="36"/>
+    <col width="27" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="30" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="34" customWidth="1" min="41" max="41"/>
+    <col width="21" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,92 +532,172 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>PredictedBiologicalLanguage_Core</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PredictedBiologicalLanguage_Strict</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HockettScore</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>PredictionPredicates</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PredictionFail</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>HasIdentity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>IsParsed</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ResolvesToAnAST</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>HasLinearDecodingPressure</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>IsStableOntologyReference</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>IsLiveOntologyEditor</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>IsOpenWorld</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>IsClosedWorld</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>DistanceFromConcept</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>IsOpenClosedWorldConflicted</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>DimensionalityWhileEditing</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>RelationshipToConcept</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ModelObjectFacilityLayer</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SortOrder</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasSemanticity</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasArbitrariness</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasDiscreteness</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasDualityOfPatterning</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasProductivity</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasDisplacement</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasCulturalTransmission</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasInterchangeability</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasFeedback</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasBroadcastTransmission</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasRapidFading</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_IsEvolvedCommunicationSystem</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_PrimaryModality</t>
         </is>
       </c>
     </row>
@@ -636,67 +732,117 @@
       <c r="H2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="M2" s="3" t="n"/>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Natural Language</t>
         </is>
       </c>
-      <c r="L2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V2" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X2" s="3" t="inlineStr">
+      <c r="AA2" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
-        <v>1</v>
+      <c r="AC2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -730,28 +876,28 @@
       <c r="H3" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="M3" s="3" t="n"/>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Physical Object</t>
         </is>
       </c>
-      <c r="L3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O3" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="2" t="b">
         <v>0</v>
@@ -763,35 +909,81 @@
         <v>0</v>
       </c>
       <c r="S3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X3" s="3" t="inlineStr">
+      <c r="AA3" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="AC3" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AD3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -824,67 +1016,117 @@
       <c r="H4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Natural Language</t>
         </is>
       </c>
-      <c r="L4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V4" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="Y4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="AC4" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="AD4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -918,31 +1160,31 @@
       <c r="H5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; Requires Parsing &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="M5" s="3" t="n"/>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O5" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="b">
         <v>0</v>
@@ -951,35 +1193,81 @@
         <v>0</v>
       </c>
       <c r="S5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X5" s="3" t="inlineStr">
+      <c r="AA5" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="AC5" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="AD5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1012,67 +1300,117 @@
       <c r="H6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="I6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="M6" s="3" t="n"/>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Natural Language</t>
         </is>
       </c>
-      <c r="L6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O6" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="Y6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X6" s="3" t="inlineStr">
+      <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="AC6" s="2" t="n">
         <v>5</v>
+      </c>
+      <c r="AD6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="2" t="inlineStr">
+        <is>
+          <t>VisualGestural</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1106,31 +1444,31 @@
       <c r="H7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="I7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; No Parsing Neede &amp; Describes the thing &amp; No Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O7" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="b">
         <v>1</v>
@@ -1141,33 +1479,79 @@
       <c r="S7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U7" s="2" t="n">
+      <c r="T7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="Y7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="AC7" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="AD7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1200,68 +1584,114 @@
       <c r="H8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="M8" s="3" t="n"/>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O8" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U8" s="2" t="n">
+      <c r="T8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="Y8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="n">
+      <c r="AC8" s="2" t="n">
         <v>7</v>
       </c>
+      <c r="AD8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1294,72 +1724,118 @@
       <c r="H9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="I9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; Requires Parsing &amp; Is the Thing &amp; No Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>Falsifier A Isn't a Family Feud Language, but Is marked as a 'Language Candidate.'</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>MISSING: Have you seen this Language?</t>
         </is>
       </c>
-      <c r="L9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O9" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X9" s="3" t="inlineStr">
+      <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="n">
+      <c r="AC9" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="AD9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1392,72 +1868,118 @@
       <c r="H10" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t>Falsifier B Is a Family Feud Language, but Is Not marked as a 'Language Candidate.'</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>MISSING: Have you seen this Language?</t>
         </is>
       </c>
-      <c r="L10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O10" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="Y10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X10" s="3" t="inlineStr">
+      <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="n">
+      <c r="AC10" s="2" t="n">
         <v>9</v>
       </c>
+      <c r="AD10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1490,26 +2012,26 @@
       <c r="H11" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; Has Linear Decoding Pressure &amp; No AST, Not 'Ontology' AND Can Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="M11" s="3" t="n"/>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Physical Object</t>
         </is>
       </c>
-      <c r="L11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O11" s="2" t="b">
         <v>1</v>
       </c>
@@ -1520,38 +2042,84 @@
         <v>0</v>
       </c>
       <c r="R11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X11" s="3" t="inlineStr">
+      <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z11" s="2" t="n">
+      <c r="AC11" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="AD11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1584,68 +2152,114 @@
       <c r="H12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I12" s="3" t="inlineStr">
+      <c r="I12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J12" s="3" t="n"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="M12" s="3" t="n"/>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="Y12" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X12" s="3" t="inlineStr">
+      <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z12" s="2" t="n">
+      <c r="AC12" s="2" t="n">
         <v>11</v>
       </c>
+      <c r="AD12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1678,68 +2292,114 @@
       <c r="H13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I13" s="3" t="inlineStr">
+      <c r="I13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; Requires Parsing &amp; Is the Thing &amp; Has Linear Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X13" s="3" t="inlineStr">
+      <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y13" s="2" t="inlineStr">
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z13" s="2" t="n">
+      <c r="AC13" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="AD13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1772,68 +2432,114 @@
       <c r="H14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="M14" s="3" t="n"/>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O14" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q14" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V14" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="Y14" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X14" s="3" t="inlineStr">
+      <c r="AA14" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z14" s="2" t="n">
+      <c r="AC14" s="2" t="n">
         <v>13</v>
       </c>
+      <c r="AD14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1866,26 +2572,26 @@
       <c r="H15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I15" s="3" t="inlineStr">
+      <c r="I15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; Resolves to AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="M15" s="3" t="n"/>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O15" s="2" t="b">
         <v>0</v>
       </c>
@@ -1901,33 +2607,79 @@
       <c r="S15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X15" s="3" t="inlineStr">
+      <c r="AA15" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="n">
+      <c r="AC15" s="2" t="n">
         <v>14</v>
       </c>
+      <c r="AD15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1960,68 +2712,114 @@
       <c r="H16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I16" s="3" t="inlineStr">
+      <c r="I16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="M16" s="3" t="n"/>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N16" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O16" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="Y16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X16" s="3" t="inlineStr">
+      <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z16" s="2" t="n">
+      <c r="AC16" s="2" t="n">
         <v>15</v>
       </c>
+      <c r="AD16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2054,68 +2852,114 @@
       <c r="H17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J17" s="3" t="n"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="M17" s="3" t="n"/>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P17" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X17" s="3" t="inlineStr">
+      <c r="AA17" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="n">
+      <c r="AC17" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="AD17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2148,68 +2992,114 @@
       <c r="H18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="M18" s="3" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Natural Language</t>
         </is>
       </c>
-      <c r="L18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O18" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q18" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U18" s="2" t="n">
+      <c r="T18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="Y18" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X18" s="3" t="inlineStr">
+      <c r="AA18" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y18" s="2" t="inlineStr">
+      <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z18" s="2" t="n">
+      <c r="AC18" s="2" t="n">
         <v>17</v>
       </c>
+      <c r="AD18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2242,34 +3132,34 @@
       <c r="H19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; Requires Parsing &amp; Is the Thing &amp; No Decoding Pressure &amp; Resolves to AST, Not 'Ontology' AND Can Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Physical event</t>
         </is>
       </c>
-      <c r="L19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N19" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="2" t="b">
         <v>0</v>
@@ -2277,33 +3167,79 @@
       <c r="S19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X19" s="3" t="inlineStr">
+      <c r="AA19" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="n">
+      <c r="AC19" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="AD19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2336,68 +3272,114 @@
       <c r="H20" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I20" s="3" t="inlineStr">
+      <c r="I20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="M20" s="3" t="n"/>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O20" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q20" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="Y20" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X20" s="3" t="inlineStr">
+      <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="n">
+      <c r="AC20" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="AD20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2430,31 +3412,31 @@
       <c r="H21" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I21" s="3" t="inlineStr">
+      <c r="I21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Is Stable Ontology AND Can Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J21" s="3" t="n"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="M21" s="3" t="n"/>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Physical Object</t>
         </is>
       </c>
-      <c r="L21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O21" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="2" t="b">
         <v>0</v>
@@ -2463,35 +3445,81 @@
         <v>0</v>
       </c>
       <c r="S21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X21" s="3" t="inlineStr">
+      <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="n">
+      <c r="AC21" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="AD21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2524,68 +3552,114 @@
       <c r="H22" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="M22" s="3" t="n"/>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N22" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q22" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V22" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="Y22" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X22" s="3" t="inlineStr">
+      <c r="AA22" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="n">
+      <c r="AC22" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="AD22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2618,34 +3692,34 @@
       <c r="H23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I23" s="3" t="inlineStr">
+      <c r="I23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>No Syntax &amp; Requires Parsing &amp; Is the Thing &amp; No Decoding Pressure &amp; Resolves to AST, Not 'Ontology' AND Can't Be Held, Has Identity</t>
         </is>
       </c>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O23" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="2" t="b">
         <v>0</v>
@@ -2653,33 +3727,79 @@
       <c r="S23" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="U23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X23" s="3" t="inlineStr">
+      <c r="AA23" s="3" t="inlineStr">
         <is>
           <t>IsMirrorOf</t>
         </is>
       </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z23" s="2" t="n">
+      <c r="AC23" s="2" t="n">
         <v>22</v>
       </c>
+      <c r="AD23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2712,38 +3832,38 @@
       <c r="H24" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>Has Syntax &amp; Requires Parsing &amp; Describes the thing &amp; Has Linear Decoding Pressure &amp; Resolves to AST, Is Stable Ontology AND Can't Be Held, Has no Identity</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve"> - Open World vs. Closed World Conflict.</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>MISSING: Have you seen this Language?</t>
         </is>
       </c>
-      <c r="L24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O24" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="2" t="b">
         <v>1</v>
@@ -2751,33 +3871,1427 @@
       <c r="S24" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="U24" s="2" t="n">
+      <c r="T24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="Y24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X24" s="3" t="inlineStr">
+      <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="n">
+      <c r="AC24" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="AD24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>honeybee-waggle-dance</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Honeybee Waggle Dance</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Is Honeybee Waggle Dance a language?</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP25" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>vervet-monkey-alarm-calls</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Vervet Monkey Alarm Calls</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Is Vervet Monkey Alarm Calls a language?</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="n"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP26" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>songbird-song-learned-dialects</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Songbird Song (learned dialects)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Is Songbird Song (learned dialects) a language?</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Has Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="n"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP27" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>killer-whale-pod-dialects</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Killer Whale Pod Dialects</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Is Killer Whale Pod Dialects a language?</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="n"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>dolphin-signature-whistles</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Dolphin Signature Whistles</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Is Dolphin Signature Whistles a language?</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="n"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP29" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ant-pheromone-trail-system</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Ant Pheromone Trail System</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>Is Ant Pheromone Trail System a language?</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="n"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP30" s="2" t="inlineStr">
+        <is>
+          <t>Tactile</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>cuttlefish-chromatophore-displays</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Cuttlefish Chromatophore Displays</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Is Cuttlefish Chromatophore Displays a language?</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; No Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="n"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP31" s="2" t="inlineStr">
+        <is>
+          <t>VisualGestural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>nicaraguan-sign-language-early-cohort</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Nicaraguan Sign Language (early cohort)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Is Nicaraguan Sign Language (early cohort) a language?</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; Has Linear Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="n"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP32" s="2" t="inlineStr">
+        <is>
+          <t>VisualGestural</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>homesign-single-child</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Homesign (single child)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Is Homesign (single child) a language?</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; Has Linear Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>bonobo-lexigram-keyboard-communication</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Bonobo/Lexigram Keyboard Communication</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Is Bonobo/Lexigram Keyboard Communication a language?</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>No Syntax &amp; No Parsing Neede &amp; Is the Thing &amp; Has Linear Decoding Pressure &amp; No AST, Not 'Ontology' AND Can't Be Held, Has no Identity</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="n"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>IsDescriptionOf</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3804,7 +6318,39 @@
 BEGIN
   RETURN ('Is ' || (SELECT NULLIF(name, '''') FROM language_candidates WHERE language_candidate_id = p_language_candidate_id) || ' a language?')::text;
 END;
-$function$
+$function$;
+CREATE OR REPLACE FUNCTION public.calc_language_candidates_bio_hockett_score(p_language_candidate_id text)
+ RETURNS integer
+ LANGUAGE plpgsql
+ STABLE SECURITY DEFINER
+AS $function$
+DECLARE
+    candidate_record RECORD;
+BEGIN
+    -- Select the required attributes for the given language candidate ID
+    SELECT bio_has_semanticity, bio_has_arbitrariness, bio_has_discreteness, 
+           bio_has_duality_of_patterning, bio_has_productivity, 
+           bio_has_displacement, bio_has_cultural_transmission, 
+           bio_has_interchangeability, bio_has_feedback, 
+           bio_has_broadcast_transmission, bio_has_rapid_fading
+    INTO candidate_record
+    FROM language_candidates
+    WHERE language_candidate_id = p_language_candidate_id;
+    -- Calculate and return the Hockett score by summing up the boolean attributes
+    RETURN 
+        COALESCE(candidate_record.bio_has_semanticity, FALSE)::int +
+        COALESCE(candidate_record.bio_has_arbitrariness, FALSE)::int +
+        COALESCE(candidate_record.bio_has_discreteness, FALSE)::int +
+        COALESCE(candidate_record.bio_has_duality_of_patterning, FALSE)::int +
+        COALESCE(candidate_record.bio_has_productivity, FALSE)::int +
+        COALESCE(candidate_record.bio_has_displacement, FALSE)::int +
+        COALESCE(candidate_record.bio_has_cultural_transmission, FALSE)::int +
+        COALESCE(candidate_record.bio_has_interchangeability, FALSE)::int +
+        COALESCE(candidate_record.bio_has_feedback, FALSE)::int +
+        COALESCE(candidate_record.bio_has_broadcast_transmission, FALSE)::int +
+        COALESCE(candidate_record.bio_has_rapid_fading, FALSE)::int;
+END;
+$function$;
 </t>
         </is>
       </c>
